--- a/Commodity_Data.xlsx
+++ b/Commodity_Data.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matth\OneDrive\Documents\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B536412-B305-4E5D-9DC9-7BAF87AA0145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97E5286-05A6-4BF0-B68D-B28203069C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1DBAD3D6-EA21-4CA8-ACD3-E65D1F41F517}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1DBAD3D6-EA21-4CA8-ACD3-E65D1F41F517}"/>
   </bookViews>
   <sheets>
     <sheet name="ReadMe" sheetId="3" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Data" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Commodity_Data.xlsx
+++ b/Commodity_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matth\OneDrive\Documents\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97E5286-05A6-4BF0-B68D-B28203069C4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE304950-8132-444E-9961-7E8D993697C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1DBAD3D6-EA21-4CA8-ACD3-E65D1F41F517}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="31">
   <si>
     <t>Year</t>
   </si>
@@ -51,12 +51,6 @@
     <t>Subsidy</t>
   </si>
   <si>
-    <t>Land Price</t>
-  </si>
-  <si>
-    <t>Rent Price</t>
-  </si>
-  <si>
     <t>ILLINOIS</t>
   </si>
   <si>
@@ -66,370 +60,76 @@
     <t>CORN</t>
   </si>
   <si>
-    <t>550648</t>
-  </si>
-  <si>
-    <t>1484868</t>
-  </si>
-  <si>
-    <t>782076</t>
-  </si>
-  <si>
-    <t>1319481</t>
-  </si>
-  <si>
-    <t>2146448</t>
-  </si>
-  <si>
-    <t>3168211</t>
-  </si>
-  <si>
-    <t>1700542</t>
-  </si>
-  <si>
-    <t>435642</t>
-  </si>
-  <si>
-    <t>337918</t>
-  </si>
-  <si>
-    <t>279977</t>
-  </si>
-  <si>
     <t>INDIANA</t>
-  </si>
-  <si>
-    <t>291436</t>
-  </si>
-  <si>
-    <t>816908</t>
-  </si>
-  <si>
-    <t>479334</t>
-  </si>
-  <si>
-    <t>648139</t>
-  </si>
-  <si>
-    <t>1085671</t>
-  </si>
-  <si>
-    <t>1611504</t>
-  </si>
-  <si>
-    <t>761978</t>
-  </si>
-  <si>
-    <t>181507</t>
-  </si>
-  <si>
-    <t>147084</t>
-  </si>
-  <si>
-    <t>120621</t>
   </si>
   <si>
     <t>IOWA</t>
   </si>
   <si>
-    <t>1859358</t>
-  </si>
-  <si>
-    <t>1445109</t>
-  </si>
-  <si>
-    <t>887941</t>
-  </si>
-  <si>
-    <t>1486059</t>
-  </si>
-  <si>
-    <t>2551496</t>
-  </si>
-  <si>
-    <t>4403728</t>
-  </si>
-  <si>
-    <t>2452757</t>
-  </si>
-  <si>
-    <t>1112927</t>
-  </si>
-  <si>
-    <t>761061</t>
-  </si>
-  <si>
-    <t>708496</t>
-  </si>
-  <si>
     <t>KENTUCKY</t>
-  </si>
-  <si>
-    <t>168606</t>
-  </si>
-  <si>
-    <t>168535</t>
-  </si>
-  <si>
-    <t>217560</t>
-  </si>
-  <si>
-    <t>203388</t>
-  </si>
-  <si>
-    <t>405695</t>
-  </si>
-  <si>
-    <t>829833</t>
-  </si>
-  <si>
-    <t>509060</t>
-  </si>
-  <si>
-    <t>169754</t>
-  </si>
-  <si>
-    <t>164919</t>
-  </si>
-  <si>
-    <t>165763</t>
   </si>
   <si>
     <t>MICHIGAN</t>
   </si>
   <si>
-    <t>247093</t>
-  </si>
-  <si>
-    <t>255540</t>
-  </si>
-  <si>
-    <t>257598</t>
-  </si>
-  <si>
-    <t>291609</t>
-  </si>
-  <si>
-    <t>475234</t>
-  </si>
-  <si>
-    <t>1158015</t>
-  </si>
-  <si>
-    <t>504835</t>
-  </si>
-  <si>
-    <t>188987</t>
-  </si>
-  <si>
-    <t>151903</t>
-  </si>
-  <si>
-    <t>191978</t>
-  </si>
-  <si>
     <t>MINNESOTA</t>
-  </si>
-  <si>
-    <t>1289339</t>
-  </si>
-  <si>
-    <t>846621</t>
-  </si>
-  <si>
-    <t>591926</t>
-  </si>
-  <si>
-    <t>1038238</t>
-  </si>
-  <si>
-    <t>1646172</t>
-  </si>
-  <si>
-    <t>3335343</t>
-  </si>
-  <si>
-    <t>1915203</t>
-  </si>
-  <si>
-    <t>933806</t>
-  </si>
-  <si>
-    <t>533168</t>
-  </si>
-  <si>
-    <t>429943</t>
   </si>
   <si>
     <t>MISSOURI</t>
   </si>
   <si>
-    <t>276246</t>
-  </si>
-  <si>
-    <t>573593</t>
-  </si>
-  <si>
-    <t>543524</t>
-  </si>
-  <si>
-    <t>728534</t>
-  </si>
-  <si>
-    <t>1365283</t>
-  </si>
-  <si>
-    <t>1834398</t>
-  </si>
-  <si>
-    <t>1229432</t>
-  </si>
-  <si>
-    <t>511202</t>
-  </si>
-  <si>
-    <t>530920</t>
-  </si>
-  <si>
-    <t>342187</t>
-  </si>
-  <si>
     <t>NEBRASKA</t>
-  </si>
-  <si>
-    <t>1049863</t>
-  </si>
-  <si>
-    <t>1117144</t>
-  </si>
-  <si>
-    <t>1031861</t>
-  </si>
-  <si>
-    <t>862170</t>
-  </si>
-  <si>
-    <t>1385170</t>
-  </si>
-  <si>
-    <t>2999645</t>
-  </si>
-  <si>
-    <t>1575044</t>
-  </si>
-  <si>
-    <t>607933</t>
-  </si>
-  <si>
-    <t>655353</t>
-  </si>
-  <si>
-    <t>512097</t>
   </si>
   <si>
     <t>OHIO</t>
   </si>
   <si>
-    <t>403885</t>
-  </si>
-  <si>
-    <t>619660</t>
-  </si>
-  <si>
-    <t>460379</t>
-  </si>
-  <si>
-    <t>560230</t>
-  </si>
-  <si>
-    <t>900414</t>
-  </si>
-  <si>
-    <t>1307094</t>
-  </si>
-  <si>
-    <t>780653</t>
-  </si>
-  <si>
-    <t>209420</t>
-  </si>
-  <si>
-    <t>229694</t>
-  </si>
-  <si>
-    <t>218582</t>
-  </si>
-  <si>
     <t>WISCONSIN</t>
   </si>
   <si>
-    <t>403506</t>
+    <t xml:space="preserve">All raw data were obtained from USDA QuickStats (September 2025). </t>
   </si>
   <si>
-    <t>373103</t>
+    <t>Derived variables are constructed using documented methods (see project documentation).</t>
   </si>
   <si>
-    <t>172637</t>
+    <t>Soybean_Yield</t>
   </si>
   <si>
-    <t>377725</t>
+    <t>Corn_Yield</t>
   </si>
   <si>
-    <t>619371</t>
+    <t>Corn_Price</t>
   </si>
   <si>
-    <t>1914611</t>
+    <t>Land_Value_per_acre</t>
   </si>
   <si>
-    <t>958969</t>
+    <t>Cash_Rent_Per_Acre</t>
   </si>
   <si>
-    <t>242937</t>
+    <t>Total_Soybean_Production</t>
   </si>
   <si>
-    <t>428463</t>
+    <t>Soybean_Revenue</t>
   </si>
   <si>
-    <t>167600</t>
+    <t>Corn_Revenue</t>
   </si>
   <si>
-    <t>Total Income</t>
+    <t>Total_Corn_Production</t>
   </si>
   <si>
-    <t>Corn Planted</t>
+    <t>Soybean_and_Corn_Revenue</t>
   </si>
   <si>
-    <t>Corn Yield</t>
+    <t>Soybean_Acres</t>
   </si>
   <si>
-    <t>Total Corn Yield</t>
+    <t>Corn_Acres</t>
   </si>
   <si>
-    <t>Corn Price</t>
-  </si>
-  <si>
-    <t>Soybeans Planted</t>
-  </si>
-  <si>
-    <t>Soybeans Yield</t>
-  </si>
-  <si>
-    <t>Total Soybeans Yield</t>
-  </si>
-  <si>
-    <t>Soybeans Price</t>
-  </si>
-  <si>
-    <t>Soybean Income</t>
-  </si>
-  <si>
-    <t>Corn Income</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All data in this spreadsheet was gathered directly from USDA Quickstats in September of 2025 with exception of colums F H L N and R </t>
-  </si>
-  <si>
-    <t xml:space="preserve">of which were calculated from data which was gathered from Quickstats. More info on calculations can be found on the poster. </t>
+    <t>Soybean_Price</t>
   </si>
 </sst>
 </file>
@@ -497,10 +197,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -839,56 +539,56 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
+      <c r="A1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
     </row>
     <row r="2" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
-      <c r="V2" s="4"/>
+      <c r="A2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -900,11 +600,11 @@
   <dimension ref="A1:R101"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="10.33203125" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="13.21875" customWidth="1"/>
     <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="12.6640625" customWidth="1"/>
     <col min="12" max="12" width="11" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="11" bestFit="1" customWidth="1"/>
@@ -922,49 +622,49 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="F1" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="G1" t="s">
-        <v>126</v>
+        <v>30</v>
       </c>
       <c r="H1" t="s">
-        <v>127</v>
+        <v>24</v>
       </c>
       <c r="I1" t="s">
         <v>2</v>
       </c>
       <c r="J1" t="s">
-        <v>119</v>
+        <v>29</v>
       </c>
       <c r="K1" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="L1" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="M1" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="N1" t="s">
-        <v>128</v>
+        <v>25</v>
       </c>
       <c r="O1" t="s">
         <v>3</v>
       </c>
       <c r="P1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="Q1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="R1" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -972,12 +672,12 @@
         <v>2024</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1">
         <v>10800000</v>
       </c>
       <c r="E2">
@@ -995,9 +695,9 @@
         <v>7119360000.000001</v>
       </c>
       <c r="I2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J2" s="3">
+        <v>6</v>
+      </c>
+      <c r="J2" s="1">
         <v>10800000</v>
       </c>
       <c r="K2">
@@ -1014,8 +714,8 @@
         <f>L2*M2</f>
         <v>6974100000</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>18</v>
+      <c r="O2" s="3">
+        <v>279977</v>
       </c>
       <c r="P2">
         <v>7580</v>
@@ -1024,7 +724,7 @@
         <v>228</v>
       </c>
       <c r="R2">
-        <f>F2*G2+L2*M2</f>
+        <f>N2+H2</f>
         <v>14093460000</v>
       </c>
     </row>
@@ -1033,12 +733,12 @@
         <v>2024</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="3">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1">
         <v>5800000</v>
       </c>
       <c r="E3">
@@ -1056,9 +756,9 @@
         <v>3558880000</v>
       </c>
       <c r="I3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J3" s="3">
+        <v>6</v>
+      </c>
+      <c r="J3" s="1">
         <v>5200000</v>
       </c>
       <c r="K3">
@@ -1075,8 +775,8 @@
         <f t="shared" ref="N3:N66" si="3">L3*M3</f>
         <v>3057600000</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>29</v>
+      <c r="O3" s="3">
+        <v>120621</v>
       </c>
       <c r="P3">
         <v>6780</v>
@@ -1085,7 +785,7 @@
         <v>197</v>
       </c>
       <c r="R3">
-        <f t="shared" ref="R3:R66" si="4">F3*G3+L3*M3</f>
+        <f>N3+H3</f>
         <v>6616480000</v>
       </c>
     </row>
@@ -1094,12 +794,12 @@
         <v>2024</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="3">
+        <v>5</v>
+      </c>
+      <c r="D4" s="1">
         <v>10050000</v>
       </c>
       <c r="E4">
@@ -1117,9 +817,9 @@
         <v>6030000000</v>
       </c>
       <c r="I4" t="s">
-        <v>8</v>
-      </c>
-      <c r="J4" s="3">
+        <v>6</v>
+      </c>
+      <c r="J4" s="1">
         <v>12900000</v>
       </c>
       <c r="K4">
@@ -1136,8 +836,8 @@
         <f t="shared" si="3"/>
         <v>8718336000</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>40</v>
+      <c r="O4" s="3">
+        <v>708496</v>
       </c>
       <c r="P4">
         <v>7860</v>
@@ -1146,7 +846,7 @@
         <v>250</v>
       </c>
       <c r="R4">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="R4:R67" si="4">N4+H4</f>
         <v>14748336000</v>
       </c>
     </row>
@@ -1155,12 +855,12 @@
         <v>2024</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="3">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1">
         <v>2050000</v>
       </c>
       <c r="E5">
@@ -1178,9 +878,9 @@
         <v>1043040000</v>
       </c>
       <c r="I5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J5" s="3">
+        <v>6</v>
+      </c>
+      <c r="J5" s="1">
         <v>1370000</v>
       </c>
       <c r="K5">
@@ -1197,8 +897,8 @@
         <f t="shared" si="3"/>
         <v>914283200</v>
       </c>
-      <c r="O5" s="1" t="s">
-        <v>51</v>
+      <c r="O5" s="3">
+        <v>165763</v>
       </c>
       <c r="P5">
         <v>3860</v>
@@ -1216,12 +916,12 @@
         <v>2024</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="3">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1">
         <v>2230000</v>
       </c>
       <c r="E6">
@@ -1239,9 +939,9 @@
         <v>1158262000</v>
       </c>
       <c r="I6" t="s">
-        <v>8</v>
-      </c>
-      <c r="J6" s="3">
+        <v>6</v>
+      </c>
+      <c r="J6" s="1">
         <v>2300000</v>
       </c>
       <c r="K6">
@@ -1258,8 +958,8 @@
         <f t="shared" si="3"/>
         <v>1352538000</v>
       </c>
-      <c r="O6" s="1" t="s">
-        <v>62</v>
+      <c r="O6" s="3">
+        <v>191978</v>
       </c>
       <c r="P6">
         <v>4620</v>
@@ -1277,12 +977,12 @@
         <v>2024</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="3">
+        <v>5</v>
+      </c>
+      <c r="D7" s="1">
         <v>7400000</v>
       </c>
       <c r="E7">
@@ -1300,9 +1000,9 @@
         <v>3330000000</v>
       </c>
       <c r="I7" t="s">
-        <v>8</v>
-      </c>
-      <c r="J7" s="3">
+        <v>6</v>
+      </c>
+      <c r="J7" s="1">
         <v>8200000</v>
       </c>
       <c r="K7">
@@ -1319,8 +1019,8 @@
         <f t="shared" si="3"/>
         <v>5195192000</v>
       </c>
-      <c r="O7" s="1" t="s">
-        <v>73</v>
+      <c r="O7" s="3">
+        <v>429943</v>
       </c>
       <c r="P7">
         <v>4860</v>
@@ -1338,12 +1038,12 @@
         <v>2024</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="3">
+        <v>5</v>
+      </c>
+      <c r="D8" s="1">
         <v>5950000</v>
       </c>
       <c r="E8">
@@ -1361,9 +1061,9 @@
         <v>2944655000</v>
       </c>
       <c r="I8" t="s">
-        <v>8</v>
-      </c>
-      <c r="J8" s="3">
+        <v>6</v>
+      </c>
+      <c r="J8" s="1">
         <v>3500000</v>
       </c>
       <c r="K8">
@@ -1380,8 +1080,8 @@
         <f t="shared" si="3"/>
         <v>1833930000</v>
       </c>
-      <c r="O8" s="1" t="s">
-        <v>84</v>
+      <c r="O8" s="3">
+        <v>342187</v>
       </c>
       <c r="P8">
         <v>3680</v>
@@ -1399,12 +1099,12 @@
         <v>2024</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="3">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1">
         <v>5300000</v>
       </c>
       <c r="E9">
@@ -1422,9 +1122,9 @@
         <v>3017025000</v>
       </c>
       <c r="I9" t="s">
-        <v>8</v>
-      </c>
-      <c r="J9" s="3">
+        <v>6</v>
+      </c>
+      <c r="J9" s="1">
         <v>10050000</v>
       </c>
       <c r="K9">
@@ -1441,8 +1141,8 @@
         <f t="shared" si="3"/>
         <v>6637522500</v>
       </c>
-      <c r="O9" s="1" t="s">
-        <v>95</v>
+      <c r="O9" s="3">
+        <v>512097</v>
       </c>
       <c r="P9">
         <v>5010</v>
@@ -1460,12 +1160,12 @@
         <v>2024</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="3">
+        <v>5</v>
+      </c>
+      <c r="D10" s="1">
         <v>5100000</v>
       </c>
       <c r="E10">
@@ -1483,9 +1183,9 @@
         <v>2601000000</v>
       </c>
       <c r="I10" t="s">
-        <v>8</v>
-      </c>
-      <c r="J10" s="3">
+        <v>6</v>
+      </c>
+      <c r="J10" s="1">
         <v>3400000</v>
       </c>
       <c r="K10">
@@ -1502,8 +1202,8 @@
         <f t="shared" si="3"/>
         <v>2023578000</v>
       </c>
-      <c r="O10" s="1" t="s">
-        <v>106</v>
+      <c r="O10" s="3">
+        <v>218582</v>
       </c>
       <c r="P10">
         <v>6030</v>
@@ -1521,12 +1221,12 @@
         <v>2024</v>
       </c>
       <c r="B11" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="3">
+        <v>5</v>
+      </c>
+      <c r="D11" s="1">
         <v>2180000</v>
       </c>
       <c r="E11">
@@ -1544,9 +1244,9 @@
         <v>1046400000</v>
       </c>
       <c r="I11" t="s">
-        <v>8</v>
-      </c>
-      <c r="J11" s="3">
+        <v>6</v>
+      </c>
+      <c r="J11" s="1">
         <v>3750000</v>
       </c>
       <c r="K11">
@@ -1563,8 +1263,8 @@
         <f t="shared" si="3"/>
         <v>2127900000</v>
       </c>
-      <c r="O11" s="2" t="s">
-        <v>117</v>
+      <c r="O11" s="4">
+        <v>167600</v>
       </c>
       <c r="P11">
         <v>4550</v>
@@ -1582,12 +1282,12 @@
         <v>2023</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="3">
+        <v>5</v>
+      </c>
+      <c r="D12" s="1">
         <v>10350000</v>
       </c>
       <c r="E12">
@@ -1605,9 +1305,9 @@
         <v>8085420000</v>
       </c>
       <c r="I12" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3">
+        <v>6</v>
+      </c>
+      <c r="J12" s="1">
         <v>11200000</v>
       </c>
       <c r="K12">
@@ -1624,8 +1324,8 @@
         <f t="shared" si="3"/>
         <v>7567952000</v>
       </c>
-      <c r="O12" s="1" t="s">
-        <v>17</v>
+      <c r="O12" s="3">
+        <v>337918</v>
       </c>
       <c r="P12">
         <v>7350</v>
@@ -1643,12 +1343,12 @@
         <v>2023</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="3">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1">
         <v>5500000</v>
       </c>
       <c r="E13">
@@ -1666,9 +1366,9 @@
         <v>4227300000</v>
       </c>
       <c r="I13" t="s">
-        <v>8</v>
-      </c>
-      <c r="J13" s="3">
+        <v>6</v>
+      </c>
+      <c r="J13" s="1">
         <v>5450000</v>
       </c>
       <c r="K13">
@@ -1685,8 +1385,8 @@
         <f t="shared" si="3"/>
         <v>3422545500</v>
       </c>
-      <c r="O13" s="1" t="s">
-        <v>28</v>
+      <c r="O13" s="3">
+        <v>147084</v>
       </c>
       <c r="P13">
         <v>6690</v>
@@ -1704,12 +1404,12 @@
         <v>2023</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="3">
+        <v>5</v>
+      </c>
+      <c r="D14" s="1">
         <v>9950000</v>
       </c>
       <c r="E14">
@@ -1727,9 +1427,9 @@
         <v>7040620000</v>
       </c>
       <c r="I14" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3">
+        <v>6</v>
+      </c>
+      <c r="J14" s="1">
         <v>13100000</v>
       </c>
       <c r="K14">
@@ -1746,8 +1446,8 @@
         <f t="shared" si="3"/>
         <v>8775690000</v>
       </c>
-      <c r="O14" s="1" t="s">
-        <v>39</v>
+      <c r="O14" s="3">
+        <v>761061</v>
       </c>
       <c r="P14">
         <v>7510</v>
@@ -1765,12 +1465,12 @@
         <v>2023</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="3">
+        <v>5</v>
+      </c>
+      <c r="D15" s="1">
         <v>1830000</v>
       </c>
       <c r="E15">
@@ -1788,9 +1488,9 @@
         <v>1288320000</v>
       </c>
       <c r="I15" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="3">
+        <v>6</v>
+      </c>
+      <c r="J15" s="1">
         <v>1600000</v>
       </c>
       <c r="K15">
@@ -1807,8 +1507,8 @@
         <f t="shared" si="3"/>
         <v>951456000</v>
       </c>
-      <c r="O15" s="1" t="s">
-        <v>50</v>
+      <c r="O15" s="3">
+        <v>164919</v>
       </c>
       <c r="P15">
         <v>3980</v>
@@ -1826,12 +1526,12 @@
         <v>2023</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="3">
+        <v>5</v>
+      </c>
+      <c r="D16" s="1">
         <v>2040000</v>
       </c>
       <c r="E16">
@@ -1849,9 +1549,9 @@
         <v>1201152000</v>
       </c>
       <c r="I16" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16" s="3">
+        <v>6</v>
+      </c>
+      <c r="J16" s="1">
         <v>2400000</v>
       </c>
       <c r="K16">
@@ -1868,8 +1568,8 @@
         <f t="shared" si="3"/>
         <v>1296192000</v>
       </c>
-      <c r="O16" s="1" t="s">
-        <v>61</v>
+      <c r="O16" s="3">
+        <v>151903</v>
       </c>
       <c r="P16">
         <v>4590</v>
@@ -1887,12 +1587,12 @@
         <v>2023</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" s="3">
+        <v>5</v>
+      </c>
+      <c r="D17" s="1">
         <v>7350000</v>
       </c>
       <c r="E17">
@@ -1910,9 +1610,9 @@
         <v>4268880000</v>
       </c>
       <c r="I17" t="s">
-        <v>8</v>
-      </c>
-      <c r="J17" s="3">
+        <v>6</v>
+      </c>
+      <c r="J17" s="1">
         <v>8600000</v>
       </c>
       <c r="K17">
@@ -1929,8 +1629,8 @@
         <f t="shared" si="3"/>
         <v>5327958000</v>
       </c>
-      <c r="O17" s="1" t="s">
-        <v>72</v>
+      <c r="O17" s="3">
+        <v>533168</v>
       </c>
       <c r="P17">
         <v>4840</v>
@@ -1948,12 +1648,12 @@
         <v>2023</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="3">
+        <v>5</v>
+      </c>
+      <c r="D18" s="1">
         <v>5600000</v>
       </c>
       <c r="E18">
@@ -1971,9 +1671,9 @@
         <v>3333120000</v>
       </c>
       <c r="I18" t="s">
-        <v>8</v>
-      </c>
-      <c r="J18" s="3">
+        <v>6</v>
+      </c>
+      <c r="J18" s="1">
         <v>3850000</v>
       </c>
       <c r="K18">
@@ -1990,8 +1690,8 @@
         <f t="shared" si="3"/>
         <v>2133670000</v>
       </c>
-      <c r="O18" s="1" t="s">
-        <v>83</v>
+      <c r="O18" s="3">
+        <v>530920</v>
       </c>
       <c r="P18">
         <v>3570</v>
@@ -2009,12 +1709,12 @@
         <v>2023</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D19" s="3">
+        <v>5</v>
+      </c>
+      <c r="D19" s="1">
         <v>5250000</v>
       </c>
       <c r="E19">
@@ -2032,9 +1732,9 @@
         <v>3298575000</v>
       </c>
       <c r="I19" t="s">
-        <v>8</v>
-      </c>
-      <c r="J19" s="3">
+        <v>6</v>
+      </c>
+      <c r="J19" s="1">
         <v>9950000</v>
       </c>
       <c r="K19">
@@ -2051,8 +1751,8 @@
         <f t="shared" si="3"/>
         <v>5880052000</v>
       </c>
-      <c r="O19" s="1" t="s">
-        <v>94</v>
+      <c r="O19" s="3">
+        <v>655353</v>
       </c>
       <c r="P19">
         <v>4750</v>
@@ -2070,12 +1770,12 @@
         <v>2023</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="3">
+        <v>5</v>
+      </c>
+      <c r="D20" s="1">
         <v>4750000</v>
       </c>
       <c r="E20">
@@ -2093,9 +1793,9 @@
         <v>3443750000</v>
       </c>
       <c r="I20" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20" s="3">
+        <v>6</v>
+      </c>
+      <c r="J20" s="1">
         <v>3600000</v>
       </c>
       <c r="K20">
@@ -2112,8 +1812,8 @@
         <f t="shared" si="3"/>
         <v>2066364000</v>
       </c>
-      <c r="O20" s="1" t="s">
-        <v>105</v>
+      <c r="O20" s="3">
+        <v>229694</v>
       </c>
       <c r="P20">
         <v>6070</v>
@@ -2131,12 +1831,12 @@
         <v>2023</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="3">
+        <v>5</v>
+      </c>
+      <c r="D21" s="1">
         <v>2110000</v>
       </c>
       <c r="E21">
@@ -2154,9 +1854,9 @@
         <v>1334364000</v>
       </c>
       <c r="I21" t="s">
-        <v>8</v>
-      </c>
-      <c r="J21" s="3">
+        <v>6</v>
+      </c>
+      <c r="J21" s="1">
         <v>4000000</v>
       </c>
       <c r="K21">
@@ -2173,8 +1873,8 @@
         <f t="shared" si="3"/>
         <v>2335360000</v>
       </c>
-      <c r="O21" s="2" t="s">
-        <v>116</v>
+      <c r="O21" s="4">
+        <v>428463</v>
       </c>
       <c r="P21">
         <v>4660</v>
@@ -2192,12 +1892,12 @@
         <v>2022</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="3">
+        <v>5</v>
+      </c>
+      <c r="D22" s="1">
         <v>10800000</v>
       </c>
       <c r="E22">
@@ -2215,9 +1915,9 @@
         <v>9729720000</v>
       </c>
       <c r="I22" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3">
+        <v>6</v>
+      </c>
+      <c r="J22" s="1">
         <v>10800000</v>
       </c>
       <c r="K22">
@@ -2234,8 +1934,8 @@
         <f t="shared" si="3"/>
         <v>7402428000</v>
       </c>
-      <c r="O22" s="1" t="s">
-        <v>16</v>
+      <c r="O22" s="3">
+        <v>435642</v>
       </c>
       <c r="P22">
         <v>7210</v>
@@ -2253,12 +1953,12 @@
         <v>2022</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="3">
+        <v>5</v>
+      </c>
+      <c r="D23" s="1">
         <v>5850000</v>
       </c>
       <c r="E23">
@@ -2276,9 +1976,9 @@
         <v>4843800000</v>
       </c>
       <c r="I23" t="s">
-        <v>8</v>
-      </c>
-      <c r="J23" s="3">
+        <v>6</v>
+      </c>
+      <c r="J23" s="1">
         <v>5250000</v>
       </c>
       <c r="K23">
@@ -2295,8 +1995,8 @@
         <f t="shared" si="3"/>
         <v>3364200000</v>
       </c>
-      <c r="O23" s="1" t="s">
-        <v>27</v>
+      <c r="O23" s="3">
+        <v>181507</v>
       </c>
       <c r="P23">
         <v>6300</v>
@@ -2314,12 +2014,12 @@
         <v>2022</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="3">
+        <v>5</v>
+      </c>
+      <c r="D24" s="1">
         <v>10100000</v>
       </c>
       <c r="E24">
@@ -2337,9 +2037,9 @@
         <v>8390070000</v>
       </c>
       <c r="I24" t="s">
-        <v>8</v>
-      </c>
-      <c r="J24" s="3">
+        <v>6</v>
+      </c>
+      <c r="J24" s="1">
         <v>12900000</v>
       </c>
       <c r="K24">
@@ -2356,8 +2056,8 @@
         <f t="shared" si="3"/>
         <v>8625198000</v>
       </c>
-      <c r="O24" s="1" t="s">
-        <v>38</v>
+      <c r="O24" s="3">
+        <v>1112927</v>
       </c>
       <c r="P24">
         <v>7440</v>
@@ -2375,12 +2075,12 @@
         <v>2022</v>
       </c>
       <c r="B25" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="3">
+        <v>5</v>
+      </c>
+      <c r="D25" s="1">
         <v>1950000</v>
       </c>
       <c r="E25">
@@ -2398,9 +2098,9 @@
         <v>1432080000</v>
       </c>
       <c r="I25" t="s">
-        <v>8</v>
-      </c>
-      <c r="J25" s="3">
+        <v>6</v>
+      </c>
+      <c r="J25" s="1">
         <v>1420000</v>
       </c>
       <c r="K25">
@@ -2417,8 +2117,8 @@
         <f t="shared" si="3"/>
         <v>932684400</v>
       </c>
-      <c r="O25" s="1" t="s">
-        <v>49</v>
+      <c r="O25" s="3">
+        <v>169754</v>
       </c>
       <c r="P25">
         <v>4140</v>
@@ -2436,12 +2136,12 @@
         <v>2022</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="C26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="3">
+        <v>5</v>
+      </c>
+      <c r="D26" s="1">
         <v>2250000</v>
       </c>
       <c r="E26">
@@ -2459,9 +2159,9 @@
         <v>1554525000</v>
       </c>
       <c r="I26" t="s">
-        <v>8</v>
-      </c>
-      <c r="J26" s="3">
+        <v>6</v>
+      </c>
+      <c r="J26" s="1">
         <v>2300000</v>
       </c>
       <c r="K26">
@@ -2478,8 +2178,8 @@
         <f t="shared" si="3"/>
         <v>1265322000</v>
       </c>
-      <c r="O26" s="1" t="s">
-        <v>60</v>
+      <c r="O26" s="3">
+        <v>188987</v>
       </c>
       <c r="P26">
         <v>4580</v>
@@ -2497,12 +2197,12 @@
         <v>2022</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="3">
+        <v>5</v>
+      </c>
+      <c r="D27" s="1">
         <v>7450000</v>
       </c>
       <c r="E27">
@@ -2520,9 +2220,9 @@
         <v>5252250000</v>
       </c>
       <c r="I27" t="s">
-        <v>8</v>
-      </c>
-      <c r="J27" s="3">
+        <v>6</v>
+      </c>
+      <c r="J27" s="1">
         <v>8000000</v>
       </c>
       <c r="K27">
@@ -2539,8 +2239,8 @@
         <f t="shared" si="3"/>
         <v>4935360000</v>
       </c>
-      <c r="O27" s="1" t="s">
-        <v>71</v>
+      <c r="O27" s="3">
+        <v>933806</v>
       </c>
       <c r="P27">
         <v>4920</v>
@@ -2558,12 +2258,12 @@
         <v>2022</v>
       </c>
       <c r="B28" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="3">
+        <v>5</v>
+      </c>
+      <c r="D28" s="1">
         <v>6100000</v>
       </c>
       <c r="E28">
@@ -2581,9 +2281,9 @@
         <v>3996720000</v>
       </c>
       <c r="I28" t="s">
-        <v>8</v>
-      </c>
-      <c r="J28" s="3">
+        <v>6</v>
+      </c>
+      <c r="J28" s="1">
         <v>3350000</v>
       </c>
       <c r="K28">
@@ -2600,8 +2300,8 @@
         <f t="shared" si="3"/>
         <v>1941995000</v>
       </c>
-      <c r="O28" s="1" t="s">
-        <v>82</v>
+      <c r="O28" s="3">
+        <v>511202</v>
       </c>
       <c r="P28">
         <v>3560</v>
@@ -2619,12 +2319,12 @@
         <v>2022</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="3">
+        <v>5</v>
+      </c>
+      <c r="D29" s="1">
         <v>5750000</v>
       </c>
       <c r="E29">
@@ -2642,9 +2342,9 @@
         <v>4000850000</v>
       </c>
       <c r="I29" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="3">
+        <v>6</v>
+      </c>
+      <c r="J29" s="1">
         <v>9600000</v>
       </c>
       <c r="K29">
@@ -2661,8 +2361,8 @@
         <f t="shared" si="3"/>
         <v>5820960000</v>
       </c>
-      <c r="O29" s="1" t="s">
-        <v>93</v>
+      <c r="O29" s="3">
+        <v>607933</v>
       </c>
       <c r="P29">
         <v>4430</v>
@@ -2680,12 +2380,12 @@
         <v>2022</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="3">
+        <v>5</v>
+      </c>
+      <c r="D30" s="1">
         <v>5100000</v>
       </c>
       <c r="E30">
@@ -2703,9 +2403,9 @@
         <v>4075920000</v>
       </c>
       <c r="I30" t="s">
-        <v>8</v>
-      </c>
-      <c r="J30" s="3">
+        <v>6</v>
+      </c>
+      <c r="J30" s="1">
         <v>3400000</v>
       </c>
       <c r="K30">
@@ -2722,8 +2422,8 @@
         <f t="shared" si="3"/>
         <v>2172498000</v>
       </c>
-      <c r="O30" s="1" t="s">
-        <v>104</v>
+      <c r="O30" s="3">
+        <v>209420</v>
       </c>
       <c r="P30">
         <v>6150</v>
@@ -2741,12 +2441,12 @@
         <v>2022</v>
       </c>
       <c r="B31" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="3">
+        <v>5</v>
+      </c>
+      <c r="D31" s="1">
         <v>2160000</v>
       </c>
       <c r="E31">
@@ -2764,9 +2464,9 @@
         <v>1609632000</v>
       </c>
       <c r="I31" t="s">
-        <v>8</v>
-      </c>
-      <c r="J31" s="3">
+        <v>6</v>
+      </c>
+      <c r="J31" s="1">
         <v>3900000</v>
       </c>
       <c r="K31">
@@ -2783,8 +2483,8 @@
         <f t="shared" si="3"/>
         <v>2239380000</v>
       </c>
-      <c r="O31" s="2" t="s">
-        <v>115</v>
+      <c r="O31" s="4">
+        <v>242937</v>
       </c>
       <c r="P31">
         <v>4870</v>
@@ -2802,12 +2502,12 @@
         <v>2021</v>
       </c>
       <c r="B32" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="3">
+        <v>5</v>
+      </c>
+      <c r="D32" s="1">
         <v>10600000</v>
       </c>
       <c r="E32">
@@ -2825,9 +2525,9 @@
         <v>9301500000</v>
       </c>
       <c r="I32" t="s">
-        <v>8</v>
-      </c>
-      <c r="J32" s="3">
+        <v>6</v>
+      </c>
+      <c r="J32" s="1">
         <v>11000000</v>
       </c>
       <c r="K32">
@@ -2844,8 +2544,8 @@
         <f t="shared" si="3"/>
         <v>8362200000</v>
       </c>
-      <c r="O32" s="1" t="s">
-        <v>15</v>
+      <c r="O32" s="3">
+        <v>1700542</v>
       </c>
       <c r="P32">
         <v>7280</v>
@@ -2863,12 +2563,12 @@
         <v>2021</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="3">
+        <v>5</v>
+      </c>
+      <c r="D33" s="1">
         <v>5650000</v>
       </c>
       <c r="E33">
@@ -2886,9 +2586,9 @@
         <v>4508700000</v>
       </c>
       <c r="I33" t="s">
-        <v>8</v>
-      </c>
-      <c r="J33" s="3">
+        <v>6</v>
+      </c>
+      <c r="J33" s="1">
         <v>5400000</v>
       </c>
       <c r="K33">
@@ -2905,8 +2605,8 @@
         <f t="shared" si="3"/>
         <v>3857868000</v>
       </c>
-      <c r="O33" s="1" t="s">
-        <v>26</v>
+      <c r="O33" s="3">
+        <v>761978</v>
       </c>
       <c r="P33">
         <v>6210</v>
@@ -2924,12 +2624,12 @@
         <v>2021</v>
       </c>
       <c r="B34" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="3">
+        <v>5</v>
+      </c>
+      <c r="D34" s="1">
         <v>10100000</v>
       </c>
       <c r="E34">
@@ -2947,9 +2647,9 @@
         <v>8526420000</v>
       </c>
       <c r="I34" t="s">
-        <v>8</v>
-      </c>
-      <c r="J34" s="3">
+        <v>6</v>
+      </c>
+      <c r="J34" s="1">
         <v>12900000</v>
       </c>
       <c r="K34">
@@ -2966,8 +2666,8 @@
         <f t="shared" si="3"/>
         <v>9076956000</v>
       </c>
-      <c r="O34" s="1" t="s">
-        <v>37</v>
+      <c r="O34" s="3">
+        <v>2452757</v>
       </c>
       <c r="P34">
         <v>7290</v>
@@ -2985,12 +2685,12 @@
         <v>2021</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C35" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="3">
+        <v>5</v>
+      </c>
+      <c r="D35" s="1">
         <v>1850000</v>
       </c>
       <c r="E35">
@@ -3008,9 +2708,9 @@
         <v>1357160000</v>
       </c>
       <c r="I35" t="s">
-        <v>8</v>
-      </c>
-      <c r="J35" s="3">
+        <v>6</v>
+      </c>
+      <c r="J35" s="1">
         <v>1530000</v>
       </c>
       <c r="K35">
@@ -3027,8 +2727,8 @@
         <f t="shared" si="3"/>
         <v>1028160000</v>
       </c>
-      <c r="O35" s="1" t="s">
-        <v>48</v>
+      <c r="O35" s="3">
+        <v>509060</v>
       </c>
       <c r="P35">
         <v>4250</v>
@@ -3046,12 +2746,12 @@
         <v>2021</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>7</v>
-      </c>
-      <c r="D36" s="3">
+        <v>5</v>
+      </c>
+      <c r="D36" s="1">
         <v>2150000</v>
       </c>
       <c r="E36">
@@ -3069,9 +2769,9 @@
         <v>1535100000</v>
       </c>
       <c r="I36" t="s">
-        <v>8</v>
-      </c>
-      <c r="J36" s="3">
+        <v>6</v>
+      </c>
+      <c r="J36" s="1">
         <v>2350000</v>
       </c>
       <c r="K36">
@@ -3088,8 +2788,8 @@
         <f t="shared" si="3"/>
         <v>1328784000</v>
       </c>
-      <c r="O36" s="1" t="s">
-        <v>59</v>
+      <c r="O36" s="3">
+        <v>504835</v>
       </c>
       <c r="P36">
         <v>4510</v>
@@ -3107,12 +2807,12 @@
         <v>2021</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="3">
+        <v>5</v>
+      </c>
+      <c r="D37" s="1">
         <v>7650000</v>
       </c>
       <c r="E37">
@@ -3130,9 +2830,9 @@
         <v>4817970000</v>
       </c>
       <c r="I37" t="s">
-        <v>8</v>
-      </c>
-      <c r="J37" s="3">
+        <v>6</v>
+      </c>
+      <c r="J37" s="1">
         <v>8350000</v>
       </c>
       <c r="K37">
@@ -3149,8 +2849,8 @@
         <f t="shared" si="3"/>
         <v>5273359000</v>
       </c>
-      <c r="O37" s="1" t="s">
-        <v>70</v>
+      <c r="O37" s="3">
+        <v>1915203</v>
       </c>
       <c r="P37">
         <v>4950</v>
@@ -3168,12 +2868,12 @@
         <v>2021</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C38" t="s">
-        <v>7</v>
-      </c>
-      <c r="D38" s="3">
+        <v>5</v>
+      </c>
+      <c r="D38" s="1">
         <v>5700000</v>
       </c>
       <c r="E38">
@@ -3191,9 +2891,9 @@
         <v>3854340000</v>
       </c>
       <c r="I38" t="s">
-        <v>8</v>
-      </c>
-      <c r="J38" s="3">
+        <v>6</v>
+      </c>
+      <c r="J38" s="1">
         <v>3600000</v>
       </c>
       <c r="K38">
@@ -3210,8 +2910,8 @@
         <f t="shared" si="3"/>
         <v>1854720000</v>
       </c>
-      <c r="O38" s="1" t="s">
-        <v>81</v>
+      <c r="O38" s="3">
+        <v>1229432</v>
       </c>
       <c r="P38">
         <v>3490</v>
@@ -3229,12 +2929,12 @@
         <v>2021</v>
       </c>
       <c r="B39" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C39" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="3">
+        <v>5</v>
+      </c>
+      <c r="D39" s="1">
         <v>5600000</v>
       </c>
       <c r="E39">
@@ -3252,9 +2952,9 @@
         <v>4480560000</v>
       </c>
       <c r="I39" t="s">
-        <v>8</v>
-      </c>
-      <c r="J39" s="3">
+        <v>6</v>
+      </c>
+      <c r="J39" s="1">
         <v>9900000</v>
       </c>
       <c r="K39">
@@ -3271,8 +2971,8 @@
         <f t="shared" si="3"/>
         <v>6804864000</v>
       </c>
-      <c r="O39" s="1" t="s">
-        <v>92</v>
+      <c r="O39" s="3">
+        <v>1575044</v>
       </c>
       <c r="P39">
         <v>4380</v>
@@ -3290,12 +2990,12 @@
         <v>2021</v>
       </c>
       <c r="B40" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D40" s="3">
+        <v>5</v>
+      </c>
+      <c r="D40" s="1">
         <v>4900000</v>
       </c>
       <c r="E40">
@@ -3313,9 +3013,9 @@
         <v>3798480000</v>
       </c>
       <c r="I40" t="s">
-        <v>8</v>
-      </c>
-      <c r="J40" s="3">
+        <v>6</v>
+      </c>
+      <c r="J40" s="1">
         <v>3550000</v>
       </c>
       <c r="K40">
@@ -3332,8 +3032,8 @@
         <f t="shared" si="3"/>
         <v>2482799000</v>
       </c>
-      <c r="O40" s="1" t="s">
-        <v>103</v>
+      <c r="O40" s="3">
+        <v>780653</v>
       </c>
       <c r="P40">
         <v>6320</v>
@@ -3351,12 +3051,12 @@
         <v>2021</v>
       </c>
       <c r="B41" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>7</v>
-      </c>
-      <c r="D41" s="3">
+        <v>5</v>
+      </c>
+      <c r="D41" s="1">
         <v>2100000</v>
       </c>
       <c r="E41">
@@ -3374,9 +3074,9 @@
         <v>1466850000</v>
       </c>
       <c r="I41" t="s">
-        <v>8</v>
-      </c>
-      <c r="J41" s="3">
+        <v>6</v>
+      </c>
+      <c r="J41" s="1">
         <v>3950000</v>
       </c>
       <c r="K41">
@@ -3393,8 +3093,8 @@
         <f t="shared" si="3"/>
         <v>2391488000</v>
       </c>
-      <c r="O41" s="2" t="s">
-        <v>114</v>
+      <c r="O41" s="4">
+        <v>958969</v>
       </c>
       <c r="P41">
         <v>4740</v>
@@ -3412,12 +3112,12 @@
         <v>2020</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C42" t="s">
-        <v>7</v>
-      </c>
-      <c r="D42" s="3">
+        <v>5</v>
+      </c>
+      <c r="D42" s="1">
         <v>10300000</v>
       </c>
       <c r="E42">
@@ -3435,9 +3135,9 @@
         <v>6736200000</v>
       </c>
       <c r="I42" t="s">
-        <v>8</v>
-      </c>
-      <c r="J42" s="3">
+        <v>6</v>
+      </c>
+      <c r="J42" s="1">
         <v>11300000</v>
       </c>
       <c r="K42">
@@ -3454,8 +3154,8 @@
         <f t="shared" si="3"/>
         <v>7260815000</v>
       </c>
-      <c r="O42" s="1" t="s">
-        <v>14</v>
+      <c r="O42" s="3">
+        <v>3168211</v>
       </c>
       <c r="P42">
         <v>7300</v>
@@ -3473,12 +3173,12 @@
         <v>2020</v>
       </c>
       <c r="B43" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C43" t="s">
-        <v>7</v>
-      </c>
-      <c r="D43" s="3">
+        <v>5</v>
+      </c>
+      <c r="D43" s="1">
         <v>5750000</v>
       </c>
       <c r="E43">
@@ -3496,9 +3196,9 @@
         <v>3765675000</v>
       </c>
       <c r="I43" t="s">
-        <v>8</v>
-      </c>
-      <c r="J43" s="3">
+        <v>6</v>
+      </c>
+      <c r="J43" s="1">
         <v>5400000</v>
       </c>
       <c r="K43">
@@ -3515,8 +3215,8 @@
         <f t="shared" si="3"/>
         <v>3504384000</v>
       </c>
-      <c r="O43" s="1" t="s">
-        <v>25</v>
+      <c r="O43" s="3">
+        <v>1611504</v>
       </c>
       <c r="P43">
         <v>6090</v>
@@ -3534,12 +3234,12 @@
         <v>2020</v>
       </c>
       <c r="B44" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>7</v>
-      </c>
-      <c r="D44" s="3">
+        <v>5</v>
+      </c>
+      <c r="D44" s="1">
         <v>9450000</v>
       </c>
       <c r="E44">
@@ -3557,9 +3257,9 @@
         <v>5664330000</v>
       </c>
       <c r="I44" t="s">
-        <v>8</v>
-      </c>
-      <c r="J44" s="3">
+        <v>6</v>
+      </c>
+      <c r="J44" s="1">
         <v>13600000</v>
       </c>
       <c r="K44">
@@ -3576,8 +3276,8 @@
         <f t="shared" si="3"/>
         <v>9424800000</v>
       </c>
-      <c r="O44" s="1" t="s">
-        <v>36</v>
+      <c r="O44" s="3">
+        <v>4403728</v>
       </c>
       <c r="P44">
         <v>7160</v>
@@ -3595,12 +3295,12 @@
         <v>2020</v>
       </c>
       <c r="B45" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C45" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" s="3">
+        <v>5</v>
+      </c>
+      <c r="D45" s="1">
         <v>1850000</v>
       </c>
       <c r="E45">
@@ -3618,9 +3318,9 @@
         <v>1098900000</v>
       </c>
       <c r="I45" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3">
+        <v>6</v>
+      </c>
+      <c r="J45" s="1">
         <v>1470000</v>
       </c>
       <c r="K45">
@@ -3637,8 +3337,8 @@
         <f t="shared" si="3"/>
         <v>973845600</v>
       </c>
-      <c r="O45" s="1" t="s">
-        <v>47</v>
+      <c r="O45" s="3">
+        <v>829833</v>
       </c>
       <c r="P45">
         <v>4350</v>
@@ -3656,12 +3356,12 @@
         <v>2020</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="C46" t="s">
-        <v>7</v>
-      </c>
-      <c r="D46" s="3">
+        <v>5</v>
+      </c>
+      <c r="D46" s="1">
         <v>2200000</v>
       </c>
       <c r="E46">
@@ -3679,9 +3379,9 @@
         <v>1235520000</v>
       </c>
       <c r="I46" t="s">
-        <v>8</v>
-      </c>
-      <c r="J46" s="3">
+        <v>6</v>
+      </c>
+      <c r="J46" s="1">
         <v>2350000</v>
       </c>
       <c r="K46">
@@ -3698,8 +3398,8 @@
         <f t="shared" si="3"/>
         <v>1288528500</v>
       </c>
-      <c r="O46" s="1" t="s">
-        <v>58</v>
+      <c r="O46" s="3">
+        <v>1158015</v>
       </c>
       <c r="P46">
         <v>4430</v>
@@ -3717,12 +3417,12 @@
         <v>2020</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C47" t="s">
-        <v>7</v>
-      </c>
-      <c r="D47" s="3">
+        <v>5</v>
+      </c>
+      <c r="D47" s="1">
         <v>7450000</v>
       </c>
       <c r="E47">
@@ -3740,9 +3440,9 @@
         <v>4097500000</v>
       </c>
       <c r="I47" t="s">
-        <v>8</v>
-      </c>
-      <c r="J47" s="3">
+        <v>6</v>
+      </c>
+      <c r="J47" s="1">
         <v>8000000</v>
       </c>
       <c r="K47">
@@ -3759,8 +3459,8 @@
         <f t="shared" si="3"/>
         <v>4537920000</v>
       </c>
-      <c r="O47" s="1" t="s">
-        <v>69</v>
+      <c r="O47" s="3">
+        <v>3335343</v>
       </c>
       <c r="P47">
         <v>4740</v>
@@ -3778,12 +3478,12 @@
         <v>2020</v>
       </c>
       <c r="B48" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C48" t="s">
-        <v>7</v>
-      </c>
-      <c r="D48" s="3">
+        <v>5</v>
+      </c>
+      <c r="D48" s="1">
         <v>5850000</v>
       </c>
       <c r="E48">
@@ -3801,9 +3501,9 @@
         <v>3311685000</v>
       </c>
       <c r="I48" t="s">
-        <v>8</v>
-      </c>
-      <c r="J48" s="3">
+        <v>6</v>
+      </c>
+      <c r="J48" s="1">
         <v>3450000</v>
       </c>
       <c r="K48">
@@ -3820,8 +3520,8 @@
         <f t="shared" si="3"/>
         <v>1962532500</v>
       </c>
-      <c r="O48" s="1" t="s">
-        <v>80</v>
+      <c r="O48" s="3">
+        <v>1834398</v>
       </c>
       <c r="P48">
         <v>3510</v>
@@ -3839,12 +3539,12 @@
         <v>2020</v>
       </c>
       <c r="B49" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>7</v>
-      </c>
-      <c r="D49" s="3">
+        <v>5</v>
+      </c>
+      <c r="D49" s="1">
         <v>5200000</v>
       </c>
       <c r="E49">
@@ -3862,9 +3562,9 @@
         <v>3076320000</v>
       </c>
       <c r="I49" t="s">
-        <v>8</v>
-      </c>
-      <c r="J49" s="3">
+        <v>6</v>
+      </c>
+      <c r="J49" s="1">
         <v>10200000</v>
       </c>
       <c r="K49">
@@ -3881,8 +3581,8 @@
         <f t="shared" si="3"/>
         <v>6534528000</v>
       </c>
-      <c r="O49" s="1" t="s">
-        <v>91</v>
+      <c r="O49" s="3">
+        <v>2999645</v>
       </c>
       <c r="P49">
         <v>4300</v>
@@ -3900,12 +3600,12 @@
         <v>2020</v>
       </c>
       <c r="B50" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="C50" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="3">
+        <v>5</v>
+      </c>
+      <c r="D50" s="1">
         <v>4950000</v>
       </c>
       <c r="E50">
@@ -3923,9 +3623,9 @@
         <v>3076425000</v>
       </c>
       <c r="I50" t="s">
-        <v>8</v>
-      </c>
-      <c r="J50" s="3">
+        <v>6</v>
+      </c>
+      <c r="J50" s="1">
         <v>3550000</v>
       </c>
       <c r="K50">
@@ -3942,8 +3642,8 @@
         <f t="shared" si="3"/>
         <v>2276402000</v>
       </c>
-      <c r="O50" s="1" t="s">
-        <v>102</v>
+      <c r="O50" s="3">
+        <v>1307094</v>
       </c>
       <c r="P50">
         <v>6440</v>
@@ -3961,12 +3661,12 @@
         <v>2020</v>
       </c>
       <c r="B51" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>7</v>
-      </c>
-      <c r="D51" s="3">
+        <v>5</v>
+      </c>
+      <c r="D51" s="1">
         <v>2020000</v>
       </c>
       <c r="E51">
@@ -3984,9 +3684,9 @@
         <v>1092416000</v>
       </c>
       <c r="I51" t="s">
-        <v>8</v>
-      </c>
-      <c r="J51" s="3">
+        <v>6</v>
+      </c>
+      <c r="J51" s="1">
         <v>3950000</v>
       </c>
       <c r="K51">
@@ -4003,8 +3703,8 @@
         <f t="shared" si="3"/>
         <v>2249051000</v>
       </c>
-      <c r="O51" s="2" t="s">
-        <v>113</v>
+      <c r="O51" s="4">
+        <v>1914611</v>
       </c>
       <c r="P51">
         <v>4840</v>
@@ -4022,12 +3722,12 @@
         <v>2019</v>
       </c>
       <c r="B52" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C52" t="s">
-        <v>7</v>
-      </c>
-      <c r="D52" s="3">
+        <v>5</v>
+      </c>
+      <c r="D52" s="1">
         <v>9950000</v>
       </c>
       <c r="E52">
@@ -4045,9 +3745,9 @@
         <v>4749732000</v>
       </c>
       <c r="I52" t="s">
-        <v>8</v>
-      </c>
-      <c r="J52" s="3">
+        <v>6</v>
+      </c>
+      <c r="J52" s="1">
         <v>10500000</v>
       </c>
       <c r="K52">
@@ -4064,8 +3764,8 @@
         <f t="shared" si="3"/>
         <v>8944530000</v>
       </c>
-      <c r="O52" s="1" t="s">
-        <v>13</v>
+      <c r="O52" s="3">
+        <v>2146448</v>
       </c>
       <c r="P52">
         <v>7300</v>
@@ -4083,12 +3783,12 @@
         <v>2019</v>
       </c>
       <c r="B53" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C53" t="s">
-        <v>7</v>
-      </c>
-      <c r="D53" s="3">
+        <v>5</v>
+      </c>
+      <c r="D53" s="1">
         <v>5400000</v>
       </c>
       <c r="E53">
@@ -4106,9 +3806,9 @@
         <v>2456568000</v>
       </c>
       <c r="I53" t="s">
-        <v>8</v>
-      </c>
-      <c r="J53" s="3">
+        <v>6</v>
+      </c>
+      <c r="J53" s="1">
         <v>4950000</v>
       </c>
       <c r="K53">
@@ -4125,8 +3825,8 @@
         <f t="shared" si="3"/>
         <v>4304272500</v>
       </c>
-      <c r="O53" s="1" t="s">
-        <v>24</v>
+      <c r="O53" s="3">
+        <v>1085671</v>
       </c>
       <c r="P53">
         <v>5970</v>
@@ -4144,12 +3844,12 @@
         <v>2019</v>
       </c>
       <c r="B54" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C54" t="s">
-        <v>7</v>
-      </c>
-      <c r="D54" s="3">
+        <v>5</v>
+      </c>
+      <c r="D54" s="1">
         <v>9200000</v>
       </c>
       <c r="E54">
@@ -4167,9 +3867,9 @@
         <v>4290880000</v>
       </c>
       <c r="I54" t="s">
-        <v>8</v>
-      </c>
-      <c r="J54" s="3">
+        <v>6</v>
+      </c>
+      <c r="J54" s="1">
         <v>13400000</v>
       </c>
       <c r="K54">
@@ -4186,8 +3886,8 @@
         <f t="shared" si="3"/>
         <v>11005152000</v>
       </c>
-      <c r="O54" s="1" t="s">
-        <v>35</v>
+      <c r="O54" s="3">
+        <v>2551496</v>
       </c>
       <c r="P54">
         <v>6970</v>
@@ -4205,12 +3905,12 @@
         <v>2019</v>
       </c>
       <c r="B55" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C55" t="s">
-        <v>7</v>
-      </c>
-      <c r="D55" s="3">
+        <v>5</v>
+      </c>
+      <c r="D55" s="1">
         <v>1700000</v>
       </c>
       <c r="E55">
@@ -4228,9 +3928,9 @@
         <v>702236000</v>
       </c>
       <c r="I55" t="s">
-        <v>8</v>
-      </c>
-      <c r="J55" s="3">
+        <v>6</v>
+      </c>
+      <c r="J55" s="1">
         <v>1550000</v>
       </c>
       <c r="K55">
@@ -4247,8 +3947,8 @@
         <f t="shared" si="3"/>
         <v>1289103999.9999998</v>
       </c>
-      <c r="O55" s="1" t="s">
-        <v>46</v>
+      <c r="O55" s="3">
+        <v>405695</v>
       </c>
       <c r="P55">
         <v>4490</v>
@@ -4266,12 +3966,12 @@
         <v>2019</v>
       </c>
       <c r="B56" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="C56" t="s">
-        <v>7</v>
-      </c>
-      <c r="D56" s="3">
+        <v>5</v>
+      </c>
+      <c r="D56" s="1">
         <v>1760000</v>
       </c>
       <c r="E56">
@@ -4289,9 +3989,9 @@
         <v>627976800</v>
       </c>
       <c r="I56" t="s">
-        <v>8</v>
-      </c>
-      <c r="J56" s="3">
+        <v>6</v>
+      </c>
+      <c r="J56" s="1">
         <v>2000000</v>
       </c>
       <c r="K56">
@@ -4308,8 +4008,8 @@
         <f t="shared" si="3"/>
         <v>1444320000</v>
       </c>
-      <c r="O56" s="1" t="s">
-        <v>57</v>
+      <c r="O56" s="3">
+        <v>475234</v>
       </c>
       <c r="P56">
         <v>4330</v>
@@ -4327,12 +4027,12 @@
         <v>2019</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C57" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57" s="3">
+        <v>5</v>
+      </c>
+      <c r="D57" s="1">
         <v>6850000</v>
       </c>
       <c r="E57">
@@ -4350,9 +4050,9 @@
         <v>2498605999.9999995</v>
       </c>
       <c r="I57" t="s">
-        <v>8</v>
-      </c>
-      <c r="J57" s="3">
+        <v>6</v>
+      </c>
+      <c r="J57" s="1">
         <v>7800000</v>
       </c>
       <c r="K57">
@@ -4369,8 +4069,8 @@
         <f t="shared" si="3"/>
         <v>6733895999.999999</v>
       </c>
-      <c r="O57" s="1" t="s">
-        <v>68</v>
+      <c r="O57" s="3">
+        <v>1646172</v>
       </c>
       <c r="P57">
         <v>4650</v>
@@ -4388,12 +4088,12 @@
         <v>2019</v>
       </c>
       <c r="B58" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C58" t="s">
-        <v>7</v>
-      </c>
-      <c r="D58" s="3">
+        <v>5</v>
+      </c>
+      <c r="D58" s="1">
         <v>5100000</v>
       </c>
       <c r="E58">
@@ -4411,9 +4111,9 @@
         <v>2052750000</v>
       </c>
       <c r="I58" t="s">
-        <v>8</v>
-      </c>
-      <c r="J58" s="3">
+        <v>6</v>
+      </c>
+      <c r="J58" s="1">
         <v>3200000</v>
       </c>
       <c r="K58">
@@ -4430,8 +4130,8 @@
         <f t="shared" si="3"/>
         <v>2496960000</v>
       </c>
-      <c r="O58" s="1" t="s">
-        <v>79</v>
+      <c r="O58" s="3">
+        <v>1365283</v>
       </c>
       <c r="P58">
         <v>3560</v>
@@ -4449,12 +4149,12 @@
         <v>2019</v>
       </c>
       <c r="B59" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>7</v>
-      </c>
-      <c r="D59" s="3">
+        <v>5</v>
+      </c>
+      <c r="D59" s="1">
         <v>4900000</v>
       </c>
       <c r="E59">
@@ -4472,9 +4172,9 @@
         <v>2370595500</v>
       </c>
       <c r="I59" t="s">
-        <v>8</v>
-      </c>
-      <c r="J59" s="3">
+        <v>6</v>
+      </c>
+      <c r="J59" s="1">
         <v>10100000</v>
       </c>
       <c r="K59">
@@ -4491,8 +4191,8 @@
         <f t="shared" si="3"/>
         <v>8126460000</v>
       </c>
-      <c r="O59" s="1" t="s">
-        <v>90</v>
+      <c r="O59" s="3">
+        <v>1385170</v>
       </c>
       <c r="P59">
         <v>4170</v>
@@ -4510,12 +4210,12 @@
         <v>2019</v>
       </c>
       <c r="B60" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="C60" t="s">
-        <v>7</v>
-      </c>
-      <c r="D60" s="3">
+        <v>5</v>
+      </c>
+      <c r="D60" s="1">
         <v>4300000</v>
       </c>
       <c r="E60">
@@ -4533,9 +4233,9 @@
         <v>1904727999.9999998</v>
       </c>
       <c r="I60" t="s">
-        <v>8</v>
-      </c>
-      <c r="J60" s="3">
+        <v>6</v>
+      </c>
+      <c r="J60" s="1">
         <v>2800000</v>
       </c>
       <c r="K60">
@@ -4552,8 +4252,8 @@
         <f t="shared" si="3"/>
         <v>2245572000</v>
       </c>
-      <c r="O60" s="1" t="s">
-        <v>101</v>
+      <c r="O60" s="3">
+        <v>900414</v>
       </c>
       <c r="P60">
         <v>6540</v>
@@ -4571,12 +4271,12 @@
         <v>2019</v>
       </c>
       <c r="B61" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="C61" t="s">
-        <v>7</v>
-      </c>
-      <c r="D61" s="3">
+        <v>5</v>
+      </c>
+      <c r="D61" s="1">
         <v>1750000</v>
       </c>
       <c r="E61">
@@ -4594,9 +4294,9 @@
         <v>692545000</v>
       </c>
       <c r="I61" t="s">
-        <v>8</v>
-      </c>
-      <c r="J61" s="3">
+        <v>6</v>
+      </c>
+      <c r="J61" s="1">
         <v>3800000</v>
       </c>
       <c r="K61">
@@ -4613,8 +4313,8 @@
         <f t="shared" si="3"/>
         <v>2918856000.0000005</v>
       </c>
-      <c r="O61" s="2" t="s">
-        <v>112</v>
+      <c r="O61" s="4">
+        <v>619371</v>
       </c>
       <c r="P61">
         <v>4740</v>
@@ -4632,12 +4332,12 @@
         <v>2018</v>
       </c>
       <c r="B62" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C62" t="s">
-        <v>7</v>
-      </c>
-      <c r="D62" s="3">
+        <v>5</v>
+      </c>
+      <c r="D62" s="1">
         <v>10800000</v>
       </c>
       <c r="E62">
@@ -4655,9 +4355,9 @@
         <v>5993892000</v>
       </c>
       <c r="I62" t="s">
-        <v>8</v>
-      </c>
-      <c r="J62" s="3">
+        <v>6</v>
+      </c>
+      <c r="J62" s="1">
         <v>11000000</v>
       </c>
       <c r="K62">
@@ -4674,8 +4374,8 @@
         <f t="shared" si="3"/>
         <v>13243120000</v>
       </c>
-      <c r="O62" s="1" t="s">
-        <v>12</v>
+      <c r="O62" s="3">
+        <v>1319481</v>
       </c>
       <c r="P62">
         <v>7800</v>
@@ -4693,12 +4393,12 @@
         <v>2018</v>
       </c>
       <c r="B63" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C63" t="s">
-        <v>7</v>
-      </c>
-      <c r="D63" s="3">
+        <v>5</v>
+      </c>
+      <c r="D63" s="1">
         <v>6000000</v>
       </c>
       <c r="E63">
@@ -4716,9 +4416,9 @@
         <v>3011850000</v>
       </c>
       <c r="I63" t="s">
-        <v>8</v>
-      </c>
-      <c r="J63" s="3">
+        <v>6</v>
+      </c>
+      <c r="J63" s="1">
         <v>5300000</v>
       </c>
       <c r="K63">
@@ -4735,8 +4435,8 @@
         <f t="shared" si="3"/>
         <v>6273345000</v>
       </c>
-      <c r="O63" s="1" t="s">
-        <v>23</v>
+      <c r="O63" s="3">
+        <v>648139</v>
       </c>
       <c r="P63">
         <v>6420</v>
@@ -4754,12 +4454,12 @@
         <v>2018</v>
       </c>
       <c r="B64" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C64" t="s">
-        <v>7</v>
-      </c>
-      <c r="D64" s="3">
+        <v>5</v>
+      </c>
+      <c r="D64" s="1">
         <v>9950000</v>
       </c>
       <c r="E64">
@@ -4777,9 +4477,9 @@
         <v>4713912000</v>
       </c>
       <c r="I64" t="s">
-        <v>8</v>
-      </c>
-      <c r="J64" s="3">
+        <v>6</v>
+      </c>
+      <c r="J64" s="1">
         <v>13200000</v>
       </c>
       <c r="K64">
@@ -4796,8 +4496,8 @@
         <f t="shared" si="3"/>
         <v>16426079999.999998</v>
       </c>
-      <c r="O64" s="1" t="s">
-        <v>34</v>
+      <c r="O64" s="3">
+        <v>1486059</v>
       </c>
       <c r="P64">
         <v>7490</v>
@@ -4815,12 +4515,12 @@
         <v>2018</v>
       </c>
       <c r="B65" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C65" t="s">
-        <v>7</v>
-      </c>
-      <c r="D65" s="3">
+        <v>5</v>
+      </c>
+      <c r="D65" s="1">
         <v>1950000</v>
       </c>
       <c r="E65">
@@ -4838,9 +4538,9 @@
         <v>874165499.99999988</v>
       </c>
       <c r="I65" t="s">
-        <v>8</v>
-      </c>
-      <c r="J65" s="3">
+        <v>6</v>
+      </c>
+      <c r="J65" s="1">
         <v>1330000</v>
       </c>
       <c r="K65">
@@ -4857,8 +4557,8 @@
         <f t="shared" si="3"/>
         <v>1478534400</v>
       </c>
-      <c r="O65" s="1" t="s">
-        <v>45</v>
+      <c r="O65" s="3">
+        <v>203388</v>
       </c>
       <c r="P65">
         <v>4650</v>
@@ -4876,12 +4576,12 @@
         <v>2018</v>
       </c>
       <c r="B66" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="C66" t="s">
-        <v>7</v>
-      </c>
-      <c r="D66" s="3">
+        <v>5</v>
+      </c>
+      <c r="D66" s="1">
         <v>2330000</v>
       </c>
       <c r="E66">
@@ -4899,9 +4599,9 @@
         <v>944057749.99999988</v>
       </c>
       <c r="I66" t="s">
-        <v>8</v>
-      </c>
-      <c r="J66" s="3">
+        <v>6</v>
+      </c>
+      <c r="J66" s="1">
         <v>2250000</v>
       </c>
       <c r="K66">
@@ -4918,8 +4618,8 @@
         <f t="shared" si="3"/>
         <v>2294190000</v>
       </c>
-      <c r="O66" s="1" t="s">
-        <v>56</v>
+      <c r="O66" s="3">
+        <v>291609</v>
       </c>
       <c r="P66">
         <v>4470</v>
@@ -4937,12 +4637,12 @@
         <v>2018</v>
       </c>
       <c r="B67" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C67" t="s">
-        <v>7</v>
-      </c>
-      <c r="D67" s="3">
+        <v>5</v>
+      </c>
+      <c r="D67" s="1">
         <v>7750000</v>
       </c>
       <c r="E67">
@@ -4960,9 +4660,9 @@
         <v>3189900000</v>
       </c>
       <c r="I67" t="s">
-        <v>8</v>
-      </c>
-      <c r="J67" s="3">
+        <v>6</v>
+      </c>
+      <c r="J67" s="1">
         <v>7900000</v>
       </c>
       <c r="K67">
@@ -4979,8 +4679,8 @@
         <f t="shared" ref="N67:N101" si="8">L67*M67</f>
         <v>8263953000</v>
       </c>
-      <c r="O67" s="1" t="s">
-        <v>67</v>
+      <c r="O67" s="3">
+        <v>1038238</v>
       </c>
       <c r="P67">
         <v>5030</v>
@@ -4989,7 +4689,7 @@
         <v>177</v>
       </c>
       <c r="R67">
-        <f t="shared" ref="R67:R101" si="9">F67*G67+L67*M67</f>
+        <f t="shared" si="4"/>
         <v>11453853000</v>
       </c>
     </row>
@@ -4998,12 +4698,12 @@
         <v>2018</v>
       </c>
       <c r="B68" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>7</v>
-      </c>
-      <c r="D68" s="3">
+        <v>5</v>
+      </c>
+      <c r="D68" s="1">
         <v>5850000</v>
       </c>
       <c r="E68">
@@ -5021,9 +4721,9 @@
         <v>2228382000</v>
       </c>
       <c r="I68" t="s">
-        <v>8</v>
-      </c>
-      <c r="J68" s="3">
+        <v>6</v>
+      </c>
+      <c r="J68" s="1">
         <v>3500000</v>
       </c>
       <c r="K68">
@@ -5040,8 +4740,8 @@
         <f t="shared" si="8"/>
         <v>3422475000</v>
       </c>
-      <c r="O68" s="1" t="s">
-        <v>78</v>
+      <c r="O68" s="3">
+        <v>728534</v>
       </c>
       <c r="P68">
         <v>3870</v>
@@ -5050,7 +4750,7 @@
         <v>137</v>
       </c>
       <c r="R68">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="R68:R101" si="9">N68+H68</f>
         <v>5650857000</v>
       </c>
     </row>
@@ -5059,12 +4759,12 @@
         <v>2018</v>
       </c>
       <c r="B69" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C69" t="s">
-        <v>7</v>
-      </c>
-      <c r="D69" s="3">
+        <v>5</v>
+      </c>
+      <c r="D69" s="1">
         <v>5650000</v>
       </c>
       <c r="E69">
@@ -5082,9 +4782,9 @@
         <v>2687140000</v>
       </c>
       <c r="I69" t="s">
-        <v>8</v>
-      </c>
-      <c r="J69" s="3">
+        <v>6</v>
+      </c>
+      <c r="J69" s="1">
         <v>9600000</v>
       </c>
       <c r="K69">
@@ -5101,8 +4801,8 @@
         <f t="shared" si="8"/>
         <v>11099904000</v>
       </c>
-      <c r="O69" s="1" t="s">
-        <v>89</v>
+      <c r="O69" s="3">
+        <v>862170</v>
       </c>
       <c r="P69">
         <v>4660</v>
@@ -5120,12 +4820,12 @@
         <v>2018</v>
       </c>
       <c r="B70" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="C70" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70" s="3">
+        <v>5</v>
+      </c>
+      <c r="D70" s="1">
         <v>5050000</v>
       </c>
       <c r="E70">
@@ -5143,9 +4843,9 @@
         <v>2457532000</v>
       </c>
       <c r="I70" t="s">
-        <v>8</v>
-      </c>
-      <c r="J70" s="3">
+        <v>6</v>
+      </c>
+      <c r="J70" s="1">
         <v>3500000</v>
       </c>
       <c r="K70">
@@ -5162,8 +4862,8 @@
         <f t="shared" si="8"/>
         <v>3998960000</v>
       </c>
-      <c r="O70" s="1" t="s">
-        <v>100</v>
+      <c r="O70" s="3">
+        <v>560230</v>
       </c>
       <c r="P70">
         <v>6920</v>
@@ -5181,12 +4881,12 @@
         <v>2018</v>
       </c>
       <c r="B71" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="C71" t="s">
-        <v>7</v>
-      </c>
-      <c r="D71" s="3">
+        <v>5</v>
+      </c>
+      <c r="D71" s="1">
         <v>2220000</v>
       </c>
       <c r="E71">
@@ -5204,9 +4904,9 @@
         <v>904694400</v>
       </c>
       <c r="I71" t="s">
-        <v>8</v>
-      </c>
-      <c r="J71" s="3">
+        <v>6</v>
+      </c>
+      <c r="J71" s="1">
         <v>3900000</v>
       </c>
       <c r="K71">
@@ -5223,8 +4923,8 @@
         <f t="shared" si="8"/>
         <v>4212000000</v>
       </c>
-      <c r="O71" s="2" t="s">
-        <v>111</v>
+      <c r="O71" s="4">
+        <v>377725</v>
       </c>
       <c r="P71">
         <v>5240</v>
@@ -5242,12 +4942,12 @@
         <v>2017</v>
       </c>
       <c r="B72" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C72" t="s">
-        <v>7</v>
-      </c>
-      <c r="D72" s="3">
+        <v>5</v>
+      </c>
+      <c r="D72" s="1">
         <v>10600000</v>
       </c>
       <c r="E72">
@@ -5265,9 +4965,9 @@
         <v>5902080000</v>
       </c>
       <c r="I72" t="s">
-        <v>8</v>
-      </c>
-      <c r="J72" s="3">
+        <v>6</v>
+      </c>
+      <c r="J72" s="1">
         <v>11200000</v>
       </c>
       <c r="K72">
@@ -5284,8 +4984,8 @@
         <f t="shared" si="8"/>
         <v>15339520000</v>
       </c>
-      <c r="O72" s="1" t="s">
-        <v>11</v>
+      <c r="O72" s="3">
+        <v>782076</v>
       </c>
       <c r="P72">
         <v>8700</v>
@@ -5303,12 +5003,12 @@
         <v>2017</v>
       </c>
       <c r="B73" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C73" t="s">
-        <v>7</v>
-      </c>
-      <c r="D73" s="3">
+        <v>5</v>
+      </c>
+      <c r="D73" s="1">
         <v>5950000</v>
       </c>
       <c r="E73">
@@ -5326,9 +5026,9 @@
         <v>3087693000</v>
       </c>
       <c r="I73" t="s">
-        <v>8</v>
-      </c>
-      <c r="J73" s="3">
+        <v>6</v>
+      </c>
+      <c r="J73" s="1">
         <v>5350000</v>
       </c>
       <c r="K73">
@@ -5345,8 +5045,8 @@
         <f t="shared" si="8"/>
         <v>6586920000</v>
       </c>
-      <c r="O73" s="1" t="s">
-        <v>22</v>
+      <c r="O73" s="3">
+        <v>479334</v>
       </c>
       <c r="P73">
         <v>7170</v>
@@ -5364,12 +5064,12 @@
         <v>2017</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C74" t="s">
-        <v>7</v>
-      </c>
-      <c r="D74" s="3">
+        <v>5</v>
+      </c>
+      <c r="D74" s="1">
         <v>10000000</v>
       </c>
       <c r="E74">
@@ -5387,9 +5087,9 @@
         <v>5272500000</v>
       </c>
       <c r="I74" t="s">
-        <v>8</v>
-      </c>
-      <c r="J74" s="3">
+        <v>6</v>
+      </c>
+      <c r="J74" s="1">
         <v>13300000</v>
       </c>
       <c r="K74">
@@ -5406,8 +5106,8 @@
         <f t="shared" si="8"/>
         <v>17609200000</v>
       </c>
-      <c r="O74" s="1" t="s">
-        <v>33</v>
+      <c r="O74" s="3">
+        <v>887941</v>
       </c>
       <c r="P74">
         <v>8830</v>
@@ -5425,12 +5125,12 @@
         <v>2017</v>
       </c>
       <c r="B75" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C75" t="s">
-        <v>7</v>
-      </c>
-      <c r="D75" s="3">
+        <v>5</v>
+      </c>
+      <c r="D75" s="1">
         <v>1950000</v>
       </c>
       <c r="E75">
@@ -5448,9 +5148,9 @@
         <v>1002494999.9999999</v>
       </c>
       <c r="I75" t="s">
-        <v>8</v>
-      </c>
-      <c r="J75" s="3">
+        <v>6</v>
+      </c>
+      <c r="J75" s="1">
         <v>1320000</v>
       </c>
       <c r="K75">
@@ -5467,8 +5167,8 @@
         <f t="shared" si="8"/>
         <v>1383782400</v>
       </c>
-      <c r="O75" s="1" t="s">
-        <v>44</v>
+      <c r="O75" s="3">
+        <v>217560</v>
       </c>
       <c r="P75">
         <v>5200</v>
@@ -5486,12 +5186,12 @@
         <v>2017</v>
       </c>
       <c r="B76" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="C76" t="s">
-        <v>7</v>
-      </c>
-      <c r="D76" s="3">
+        <v>5</v>
+      </c>
+      <c r="D76" s="1">
         <v>2280000</v>
       </c>
       <c r="E76">
@@ -5509,9 +5209,9 @@
         <v>909891000</v>
       </c>
       <c r="I76" t="s">
-        <v>8</v>
-      </c>
-      <c r="J76" s="3">
+        <v>6</v>
+      </c>
+      <c r="J76" s="1">
         <v>2250000</v>
       </c>
       <c r="K76">
@@ -5528,8 +5228,8 @@
         <f t="shared" si="8"/>
         <v>2328480000</v>
       </c>
-      <c r="O76" s="1" t="s">
-        <v>55</v>
+      <c r="O76" s="3">
+        <v>257598</v>
       </c>
       <c r="P76">
         <v>4960</v>
@@ -5547,12 +5247,12 @@
         <v>2017</v>
       </c>
       <c r="B77" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C77" t="s">
-        <v>7</v>
-      </c>
-      <c r="D77" s="3">
+        <v>5</v>
+      </c>
+      <c r="D77" s="1">
         <v>8150000</v>
       </c>
       <c r="E77">
@@ -5570,9 +5270,9 @@
         <v>3549936250</v>
       </c>
       <c r="I77" t="s">
-        <v>8</v>
-      </c>
-      <c r="J77" s="3">
+        <v>6</v>
+      </c>
+      <c r="J77" s="1">
         <v>8050000</v>
       </c>
       <c r="K77">
@@ -5589,8 +5289,8 @@
         <f t="shared" si="8"/>
         <v>9842332500</v>
       </c>
-      <c r="O77" s="1" t="s">
-        <v>66</v>
+      <c r="O77" s="3">
+        <v>591926</v>
       </c>
       <c r="P77">
         <v>5830</v>
@@ -5608,12 +5308,12 @@
         <v>2017</v>
       </c>
       <c r="B78" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C78" t="s">
-        <v>7</v>
-      </c>
-      <c r="D78" s="3">
+        <v>5</v>
+      </c>
+      <c r="D78" s="1">
         <v>5950000</v>
       </c>
       <c r="E78">
@@ -5631,9 +5331,9 @@
         <v>2792097000</v>
       </c>
       <c r="I78" t="s">
-        <v>8</v>
-      </c>
-      <c r="J78" s="3">
+        <v>6</v>
+      </c>
+      <c r="J78" s="1">
         <v>3400000</v>
       </c>
       <c r="K78">
@@ -5650,8 +5350,8 @@
         <f t="shared" si="8"/>
         <v>3673054000</v>
       </c>
-      <c r="O78" s="1" t="s">
-        <v>77</v>
+      <c r="O78" s="3">
+        <v>543524</v>
       </c>
       <c r="P78">
         <v>4400</v>
@@ -5669,12 +5369,12 @@
         <v>2017</v>
       </c>
       <c r="B79" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C79" t="s">
-        <v>7</v>
-      </c>
-      <c r="D79" s="3">
+        <v>5</v>
+      </c>
+      <c r="D79" s="1">
         <v>5700000</v>
       </c>
       <c r="E79">
@@ -5692,9 +5392,9 @@
         <v>2975970000</v>
       </c>
       <c r="I79" t="s">
-        <v>8</v>
-      </c>
-      <c r="J79" s="3">
+        <v>6</v>
+      </c>
+      <c r="J79" s="1">
         <v>9550000</v>
       </c>
       <c r="K79">
@@ -5711,8 +5411,8 @@
         <f t="shared" si="8"/>
         <v>10667827500</v>
       </c>
-      <c r="O79" s="1" t="s">
-        <v>88</v>
+      <c r="O79" s="3">
+        <v>1031861</v>
       </c>
       <c r="P79">
         <v>5520</v>
@@ -5730,12 +5430,12 @@
         <v>2017</v>
       </c>
       <c r="B80" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="C80" t="s">
-        <v>7</v>
-      </c>
-      <c r="D80" s="3">
+        <v>5</v>
+      </c>
+      <c r="D80" s="1">
         <v>5100000</v>
       </c>
       <c r="E80">
@@ -5753,9 +5453,9 @@
         <v>2428569000</v>
       </c>
       <c r="I80" t="s">
-        <v>8</v>
-      </c>
-      <c r="J80" s="3">
+        <v>6</v>
+      </c>
+      <c r="J80" s="1">
         <v>3400000</v>
       </c>
       <c r="K80">
@@ -5772,8 +5472,8 @@
         <f t="shared" si="8"/>
         <v>3992824000</v>
       </c>
-      <c r="O80" s="1" t="s">
-        <v>99</v>
+      <c r="O80" s="3">
+        <v>460379</v>
       </c>
       <c r="P80">
         <v>7740</v>
@@ -5791,12 +5491,12 @@
         <v>2017</v>
       </c>
       <c r="B81" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="C81" t="s">
-        <v>7</v>
-      </c>
-      <c r="D81" s="3">
+        <v>5</v>
+      </c>
+      <c r="D81" s="1">
         <v>2150000</v>
       </c>
       <c r="E81">
@@ -5814,9 +5514,9 @@
         <v>953847500</v>
       </c>
       <c r="I81" t="s">
-        <v>8</v>
-      </c>
-      <c r="J81" s="3">
+        <v>6</v>
+      </c>
+      <c r="J81" s="1">
         <v>3900000</v>
       </c>
       <c r="K81">
@@ -5833,8 +5533,8 @@
         <f t="shared" si="8"/>
         <v>4289220000</v>
       </c>
-      <c r="O81" s="2" t="s">
-        <v>110</v>
+      <c r="O81" s="4">
+        <v>172637</v>
       </c>
       <c r="P81">
         <v>5940</v>
@@ -5852,12 +5552,12 @@
         <v>2016</v>
       </c>
       <c r="B82" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C82" t="s">
-        <v>7</v>
-      </c>
-      <c r="D82" s="3">
+        <v>5</v>
+      </c>
+      <c r="D82" s="1">
         <v>10100000</v>
       </c>
       <c r="E82">
@@ -5875,9 +5575,9 @@
         <v>5827902000</v>
       </c>
       <c r="I82" t="s">
-        <v>8</v>
-      </c>
-      <c r="J82" s="3">
+        <v>6</v>
+      </c>
+      <c r="J82" s="1">
         <v>11600000</v>
       </c>
       <c r="K82">
@@ -5894,8 +5594,8 @@
         <f t="shared" si="8"/>
         <v>10657616000</v>
       </c>
-      <c r="O82" s="1" t="s">
-        <v>10</v>
+      <c r="O82" s="3">
+        <v>1484868</v>
       </c>
       <c r="P82">
         <v>9250</v>
@@ -5913,12 +5613,12 @@
         <v>2016</v>
       </c>
       <c r="B83" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C83" t="s">
-        <v>7</v>
-      </c>
-      <c r="D83" s="3">
+        <v>5</v>
+      </c>
+      <c r="D83" s="1">
         <v>5650000</v>
       </c>
       <c r="E83">
@@ -5936,9 +5636,9 @@
         <v>3148038750</v>
       </c>
       <c r="I83" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3">
+        <v>6</v>
+      </c>
+      <c r="J83" s="1">
         <v>5600000</v>
       </c>
       <c r="K83">
@@ -5955,8 +5655,8 @@
         <f t="shared" si="8"/>
         <v>5115600000</v>
       </c>
-      <c r="O83" s="1" t="s">
-        <v>21</v>
+      <c r="O83" s="3">
+        <v>816908</v>
       </c>
       <c r="P83">
         <v>7620</v>
@@ -5974,12 +5674,12 @@
         <v>2016</v>
       </c>
       <c r="B84" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>7</v>
-      </c>
-      <c r="D84" s="3">
+        <v>5</v>
+      </c>
+      <c r="D84" s="1">
         <v>9500000</v>
       </c>
       <c r="E84">
@@ -5997,9 +5697,9 @@
         <v>5323800000</v>
       </c>
       <c r="I84" t="s">
-        <v>8</v>
-      </c>
-      <c r="J84" s="3">
+        <v>6</v>
+      </c>
+      <c r="J84" s="1">
         <v>13900000</v>
       </c>
       <c r="K84">
@@ -6016,8 +5716,8 @@
         <f t="shared" si="8"/>
         <v>12879879000</v>
       </c>
-      <c r="O84" s="1" t="s">
-        <v>32</v>
+      <c r="O84" s="3">
+        <v>1445109</v>
       </c>
       <c r="P84">
         <v>9410</v>
@@ -6035,12 +5735,12 @@
         <v>2016</v>
       </c>
       <c r="B85" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C85" t="s">
-        <v>7</v>
-      </c>
-      <c r="D85" s="3">
+        <v>5</v>
+      </c>
+      <c r="D85" s="1">
         <v>1790000</v>
       </c>
       <c r="E85">
@@ -6058,9 +5758,9 @@
         <v>883364999.99999988</v>
       </c>
       <c r="I85" t="s">
-        <v>8</v>
-      </c>
-      <c r="J85" s="3">
+        <v>6</v>
+      </c>
+      <c r="J85" s="1">
         <v>1500000</v>
       </c>
       <c r="K85">
@@ -6077,8 +5777,8 @@
         <f t="shared" si="8"/>
         <v>1332375000</v>
       </c>
-      <c r="O85" s="1" t="s">
-        <v>43</v>
+      <c r="O85" s="3">
+        <v>168535</v>
       </c>
       <c r="P85">
         <v>5720</v>
@@ -6096,12 +5796,12 @@
         <v>2016</v>
       </c>
       <c r="B86" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="C86" t="s">
-        <v>7</v>
-      </c>
-      <c r="D86" s="3">
+        <v>5</v>
+      </c>
+      <c r="D86" s="1">
         <v>2070000</v>
       </c>
       <c r="E86">
@@ -6119,9 +5819,9 @@
         <v>994127850</v>
       </c>
       <c r="I86" t="s">
-        <v>8</v>
-      </c>
-      <c r="J86" s="3">
+        <v>6</v>
+      </c>
+      <c r="J86" s="1">
         <v>2400000</v>
       </c>
       <c r="K86">
@@ -6138,8 +5838,8 @@
         <f t="shared" si="8"/>
         <v>1689408000.0000002</v>
       </c>
-      <c r="O86" s="1" t="s">
-        <v>54</v>
+      <c r="O86" s="3">
+        <v>255540</v>
       </c>
       <c r="P86">
         <v>5420</v>
@@ -6157,12 +5857,12 @@
         <v>2016</v>
       </c>
       <c r="B87" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C87" t="s">
-        <v>7</v>
-      </c>
-      <c r="D87" s="3">
+        <v>5</v>
+      </c>
+      <c r="D87" s="1">
         <v>7550000</v>
       </c>
       <c r="E87">
@@ -6180,9 +5880,9 @@
         <v>3623698000</v>
       </c>
       <c r="I87" t="s">
-        <v>8</v>
-      </c>
-      <c r="J87" s="3">
+        <v>6</v>
+      </c>
+      <c r="J87" s="1">
         <v>8450000</v>
       </c>
       <c r="K87">
@@ -6199,8 +5899,8 @@
         <f t="shared" si="8"/>
         <v>6909565000</v>
       </c>
-      <c r="O87" s="1" t="s">
-        <v>65</v>
+      <c r="O87" s="3">
+        <v>846621</v>
       </c>
       <c r="P87">
         <v>6310</v>
@@ -6218,12 +5918,12 @@
         <v>2016</v>
       </c>
       <c r="B88" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C88" t="s">
-        <v>7</v>
-      </c>
-      <c r="D88" s="3">
+        <v>5</v>
+      </c>
+      <c r="D88" s="1">
         <v>5600000</v>
       </c>
       <c r="E88">
@@ -6241,9 +5941,9 @@
         <v>2634240000</v>
       </c>
       <c r="I88" t="s">
-        <v>8</v>
-      </c>
-      <c r="J88" s="3">
+        <v>6</v>
+      </c>
+      <c r="J88" s="1">
         <v>3650000</v>
       </c>
       <c r="K88">
@@ -6260,8 +5960,8 @@
         <f t="shared" si="8"/>
         <v>2568870000</v>
       </c>
-      <c r="O88" s="1" t="s">
-        <v>76</v>
+      <c r="O88" s="3">
+        <v>573593</v>
       </c>
       <c r="P88">
         <v>4720</v>
@@ -6279,12 +5979,12 @@
         <v>2016</v>
       </c>
       <c r="B89" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C89" t="s">
-        <v>7</v>
-      </c>
-      <c r="D89" s="3">
+        <v>5</v>
+      </c>
+      <c r="D89" s="1">
         <v>5200000</v>
       </c>
       <c r="E89">
@@ -6302,9 +6002,9 @@
         <v>2911896000</v>
       </c>
       <c r="I89" t="s">
-        <v>8</v>
-      </c>
-      <c r="J89" s="3">
+        <v>6</v>
+      </c>
+      <c r="J89" s="1">
         <v>9850000</v>
       </c>
       <c r="K89">
@@ -6321,8 +6021,8 @@
         <f t="shared" si="8"/>
         <v>8389835999.999999</v>
       </c>
-      <c r="O89" s="1" t="s">
-        <v>87</v>
+      <c r="O89" s="3">
+        <v>1117144</v>
       </c>
       <c r="P89">
         <v>6150</v>
@@ -6340,12 +6040,12 @@
         <v>2016</v>
       </c>
       <c r="B90" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="C90" t="s">
-        <v>7</v>
-      </c>
-      <c r="D90" s="3">
+        <v>5</v>
+      </c>
+      <c r="D90" s="1">
         <v>4850000</v>
       </c>
       <c r="E90">
@@ -6363,9 +6063,9 @@
         <v>2553379500</v>
       </c>
       <c r="I90" t="s">
-        <v>8</v>
-      </c>
-      <c r="J90" s="3">
+        <v>6</v>
+      </c>
+      <c r="J90" s="1">
         <v>3550000</v>
       </c>
       <c r="K90">
@@ -6382,8 +6082,8 @@
         <f t="shared" si="8"/>
         <v>3085731000</v>
       </c>
-      <c r="O90" s="1" t="s">
-        <v>98</v>
+      <c r="O90" s="3">
+        <v>619660</v>
       </c>
       <c r="P90">
         <v>8450</v>
@@ -6401,12 +6101,12 @@
         <v>2016</v>
       </c>
       <c r="B91" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="C91" t="s">
-        <v>7</v>
-      </c>
-      <c r="D91" s="3">
+        <v>5</v>
+      </c>
+      <c r="D91" s="1">
         <v>1960000</v>
       </c>
       <c r="E91">
@@ -6424,9 +6124,9 @@
         <v>1009007999.9999999</v>
       </c>
       <c r="I91" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3">
+        <v>6</v>
+      </c>
+      <c r="J91" s="1">
         <v>4050000</v>
       </c>
       <c r="K91">
@@ -6443,8 +6143,8 @@
         <f t="shared" si="8"/>
         <v>3057912000</v>
       </c>
-      <c r="O91" s="2" t="s">
-        <v>109</v>
+      <c r="O91" s="4">
+        <v>373103</v>
       </c>
       <c r="P91">
         <v>6620</v>
@@ -6462,12 +6162,12 @@
         <v>2015</v>
       </c>
       <c r="B92" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C92" t="s">
-        <v>7</v>
-      </c>
-      <c r="D92" s="3">
+        <v>5</v>
+      </c>
+      <c r="D92" s="1">
         <v>9800000</v>
       </c>
       <c r="E92">
@@ -6485,9 +6185,9 @@
         <v>5043472000</v>
       </c>
       <c r="I92" t="s">
-        <v>8</v>
-      </c>
-      <c r="J92" s="3">
+        <v>6</v>
+      </c>
+      <c r="J92" s="1">
         <v>11700000</v>
       </c>
       <c r="K92">
@@ -6504,8 +6204,8 @@
         <f t="shared" si="8"/>
         <v>10917270000</v>
       </c>
-      <c r="O92" s="1" t="s">
-        <v>9</v>
+      <c r="O92" s="3">
+        <v>550648</v>
       </c>
       <c r="P92">
         <v>9550</v>
@@ -6523,12 +6223,12 @@
         <v>2015</v>
       </c>
       <c r="B93" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="C93" t="s">
-        <v>7</v>
-      </c>
-      <c r="D93" s="3">
+        <v>5</v>
+      </c>
+      <c r="D93" s="1">
         <v>5550000</v>
       </c>
       <c r="E93">
@@ -6546,9 +6246,9 @@
         <v>2541900000</v>
       </c>
       <c r="I93" t="s">
-        <v>8</v>
-      </c>
-      <c r="J93" s="3">
+        <v>6</v>
+      </c>
+      <c r="J93" s="1">
         <v>5650000</v>
       </c>
       <c r="K93">
@@ -6565,8 +6265,8 @@
         <f t="shared" si="8"/>
         <v>4810410000</v>
       </c>
-      <c r="O93" s="1" t="s">
-        <v>20</v>
+      <c r="O93" s="3">
+        <v>291436</v>
       </c>
       <c r="P93">
         <v>7870</v>
@@ -6584,12 +6284,12 @@
         <v>2015</v>
       </c>
       <c r="B94" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C94" t="s">
-        <v>7</v>
-      </c>
-      <c r="D94" s="3">
+        <v>5</v>
+      </c>
+      <c r="D94" s="1">
         <v>9850000</v>
       </c>
       <c r="E94">
@@ -6607,9 +6307,9 @@
         <v>4958637750</v>
       </c>
       <c r="I94" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="3">
+        <v>6</v>
+      </c>
+      <c r="J94" s="1">
         <v>13500000</v>
       </c>
       <c r="K94">
@@ -6626,8 +6326,8 @@
         <f t="shared" si="8"/>
         <v>12533400000.000002</v>
       </c>
-      <c r="O94" s="1" t="s">
-        <v>31</v>
+      <c r="O94" s="3">
+        <v>1859358</v>
       </c>
       <c r="P94">
         <v>9800</v>
@@ -6645,12 +6345,12 @@
         <v>2015</v>
       </c>
       <c r="B95" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="C95" t="s">
-        <v>7</v>
-      </c>
-      <c r="D95" s="3">
+        <v>5</v>
+      </c>
+      <c r="D95" s="1">
         <v>1840000</v>
       </c>
       <c r="E95">
@@ -6668,9 +6368,9 @@
         <v>833078400</v>
       </c>
       <c r="I95" t="s">
-        <v>8</v>
-      </c>
-      <c r="J95" s="3">
+        <v>6</v>
+      </c>
+      <c r="J95" s="1">
         <v>1400000</v>
       </c>
       <c r="K95">
@@ -6687,8 +6387,8 @@
         <f t="shared" si="8"/>
         <v>1121400000</v>
       </c>
-      <c r="O95" s="1" t="s">
-        <v>42</v>
+      <c r="O95" s="3">
+        <v>168606</v>
       </c>
       <c r="P95">
         <v>6220</v>
@@ -6706,12 +6406,12 @@
         <v>2015</v>
       </c>
       <c r="B96" t="s">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="C96" t="s">
-        <v>7</v>
-      </c>
-      <c r="D96" s="3">
+        <v>5</v>
+      </c>
+      <c r="D96" s="1">
         <v>2030000</v>
       </c>
       <c r="E96">
@@ -6729,9 +6429,9 @@
         <v>877325400</v>
       </c>
       <c r="I96" t="s">
-        <v>8</v>
-      </c>
-      <c r="J96" s="3">
+        <v>6</v>
+      </c>
+      <c r="J96" s="1">
         <v>2350000</v>
       </c>
       <c r="K96">
@@ -6748,8 +6448,8 @@
         <f t="shared" si="8"/>
         <v>1786470000</v>
       </c>
-      <c r="O96" s="1" t="s">
-        <v>53</v>
+      <c r="O96" s="3">
+        <v>247093</v>
       </c>
       <c r="P96">
         <v>5870</v>
@@ -6767,12 +6467,12 @@
         <v>2015</v>
       </c>
       <c r="B97" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="C97" t="s">
-        <v>7</v>
-      </c>
-      <c r="D97" s="3">
+        <v>5</v>
+      </c>
+      <c r="D97" s="1">
         <v>7600000</v>
       </c>
       <c r="E97">
@@ -6790,9 +6490,9 @@
         <v>3325000000</v>
       </c>
       <c r="I97" t="s">
-        <v>8</v>
-      </c>
-      <c r="J97" s="3">
+        <v>6</v>
+      </c>
+      <c r="J97" s="1">
         <v>8100000</v>
       </c>
       <c r="K97">
@@ -6809,8 +6509,8 @@
         <f t="shared" si="8"/>
         <v>6130889999.999999</v>
       </c>
-      <c r="O97" s="1" t="s">
-        <v>64</v>
+      <c r="O97" s="3">
+        <v>1289339</v>
       </c>
       <c r="P97">
         <v>6540</v>
@@ -6828,12 +6528,12 @@
         <v>2015</v>
       </c>
       <c r="B98" t="s">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="C98" t="s">
-        <v>7</v>
-      </c>
-      <c r="D98" s="3">
+        <v>5</v>
+      </c>
+      <c r="D98" s="1">
         <v>4550000</v>
       </c>
       <c r="E98">
@@ -6851,9 +6551,9 @@
         <v>1687959000</v>
       </c>
       <c r="I98" t="s">
-        <v>8</v>
-      </c>
-      <c r="J98" s="3">
+        <v>6</v>
+      </c>
+      <c r="J98" s="1">
         <v>3250000</v>
       </c>
       <c r="K98">
@@ -6870,8 +6570,8 @@
         <f t="shared" si="8"/>
         <v>2527687500</v>
       </c>
-      <c r="O98" s="1" t="s">
-        <v>75</v>
+      <c r="O98" s="3">
+        <v>276246</v>
       </c>
       <c r="P98">
         <v>4910</v>
@@ -6889,12 +6589,12 @@
         <v>2015</v>
       </c>
       <c r="B99" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>7</v>
-      </c>
-      <c r="D99" s="3">
+        <v>5</v>
+      </c>
+      <c r="D99" s="1">
         <v>5300000</v>
       </c>
       <c r="E99">
@@ -6912,9 +6612,9 @@
         <v>2662084000</v>
       </c>
       <c r="I99" t="s">
-        <v>8</v>
-      </c>
-      <c r="J99" s="3">
+        <v>6</v>
+      </c>
+      <c r="J99" s="1">
         <v>9400000</v>
       </c>
       <c r="K99">
@@ -6931,8 +6631,8 @@
         <f t="shared" si="8"/>
         <v>7864040000</v>
       </c>
-      <c r="O99" s="1" t="s">
-        <v>86</v>
+      <c r="O99" s="3">
+        <v>1049863</v>
       </c>
       <c r="P99">
         <v>6540</v>
@@ -6950,12 +6650,12 @@
         <v>2015</v>
       </c>
       <c r="B100" t="s">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="C100" t="s">
-        <v>7</v>
-      </c>
-      <c r="D100" s="3">
+        <v>5</v>
+      </c>
+      <c r="D100" s="1">
         <v>4750000</v>
       </c>
       <c r="E100">
@@ -6973,9 +6673,9 @@
         <v>2175500000</v>
       </c>
       <c r="I100" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
+        <v>6</v>
+      </c>
+      <c r="J100" s="1">
         <v>3550000</v>
       </c>
       <c r="K100">
@@ -6992,8 +6692,8 @@
         <f t="shared" si="8"/>
         <v>2670487500</v>
       </c>
-      <c r="O100" s="1" t="s">
-        <v>97</v>
+      <c r="O100" s="3">
+        <v>403885</v>
       </c>
       <c r="P100">
         <v>9270</v>
@@ -7011,12 +6711,12 @@
         <v>2015</v>
       </c>
       <c r="B101" t="s">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="C101" t="s">
-        <v>7</v>
-      </c>
-      <c r="D101" s="3">
+        <v>5</v>
+      </c>
+      <c r="D101" s="1">
         <v>1880000</v>
       </c>
       <c r="E101">
@@ -7034,9 +6734,9 @@
         <v>812413800</v>
       </c>
       <c r="I101" t="s">
-        <v>8</v>
-      </c>
-      <c r="J101" s="3">
+        <v>6</v>
+      </c>
+      <c r="J101" s="1">
         <v>4000000</v>
       </c>
       <c r="K101">
@@ -7053,8 +6753,8 @@
         <f t="shared" si="8"/>
         <v>3062400000.0000005</v>
       </c>
-      <c r="O101" s="2" t="s">
-        <v>108</v>
+      <c r="O101" s="4">
+        <v>403506</v>
       </c>
       <c r="P101">
         <v>6800</v>
